--- a/GT3_Car_Data.xlsx
+++ b/GT3_Car_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\darin\Desktop\Racing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{954195F4-5EF2-4D1E-9508-ADD2E4C465F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C20B0E9-45CF-45C6-A7EB-14512DCE0A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="23880" yWindow="-3270" windowWidth="29040" windowHeight="18240" xr2:uid="{8438E228-7A54-4973-AA5E-639F4A624053}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Car</t>
   </si>
@@ -88,6 +88,42 @@
   </si>
   <si>
     <t>Ferrari 296 GT3</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Rear-engine 4.2L flat-six (NA), highest rev limit (9,500) and power in the field. Shortest wheelbase; rear weight bias gives class-leading traction and braking stability. Aero is strong on the rear but the nose can go light at high speed. Desirable: superb corner exits, late braking, great on kerbs and in the wet. Undesirable: lift-off/trail-brake oversteer is snappy, needs patient rotation on entry, and mid-corner understeer if you rush it. Rewards a precise, experienced driver.</t>
+  </si>
+  <si>
+    <t>Front-mid 6.2L NA V8 with a long hood and heavy front weight. Big low-end torque with a low 7,800 rpm limit, so it's short-shifted and lugs well out of slow corners. Stable, low-drag aero and good top speed. Desirable: very forgiving, rides kerbs and bumps well, easy on tires, excellent beginner and endurance car. Undesirable: lazy rotation and understeer in tight, slow corners; its bulk shows in quick direction changes and hairpins.</t>
+  </si>
+  <si>
+    <t>Front-mid 5.4L NA V8 (Coyote-based) with the second-longest body in the field and a long 109 in wheelbase. Long, stable platform with efficient aero and strong straight-line speed. Desirable: very planted in high-speed corners and under braking, predictable at the limit, good traction from the linear V8. Undesirable: slow to turn in and understeers in tight hairpins and chicanes; its length makes it cumbersome at twisty, slow tracks. Best suited to fast, flowing circuits with long straights.</t>
+  </si>
+  <si>
+    <t>Mid-engine 5.2L NA V10 revving to 8,500. Short, wide car with a compact wheelbase, giving quick turn-in and strong rotation. Aero is solid with good downforce balance. Desirable: agile in slow and medium corners, strong braking, excellent in chicanes and direction changes. Undesirable: can be nervous and snap-oversteer on corner exit or over kerbs, is setup-sensitive, and punishes rough inputs. Rewards an aggressive, precise driver more than a beginner.</t>
+  </si>
+  <si>
+    <t>Mid-engine 4.0L twin-turbo V8 with the most torque in the field (492 lb-ft) and a carbon tub. Aero-heavy design with strong downforce that shines in fast corners. Desirable: excellent high-speed cornering, strong acceleration off mid-speed corners, good braking. Undesirable: turbo torque can overwhelm the rears on slow exits, and it can feel pointy and less stable over bumps and kerbs. Best on fast, smooth, flowing tracks; demands throttle discipline in slow sections.</t>
+  </si>
+  <si>
+    <t>Mid-engine 3.5L twin-turbo V6 (race car drops the road car's hybrid). Balanced mid-engine chassis with good mechanical grip and aero stability. Desirable: neutral handling, strong braking and traction, rotates well without being snappy, easy to drive consistently. Undesirable: lower rev limit (7,500) and smaller engine can leave it short of top speed on long straights, so it may struggle on power tracks depending on BoP. A good all-rounder that suits technical, twisty circuits.</t>
+  </si>
+  <si>
+    <t>Front-mid 4.0L twin-turbo V8 with a long 109 in wheelbase and a 7,000 rpm limit (joint-lowest with the BMW). Broad torque (472 lb-ft) and a short body with long wheelbase give it a stable, planted feel. Desirable: very predictable, forgiving at the limit, strong traction and braking stability, gentle on tires, good for long stints. Undesirable: some understeer in slow corners and less agile than mid-engine cars in quick direction changes. A confidence-inspiring car that suits consistent drivers.</t>
+  </si>
+  <si>
+    <t>Mid-engine 5.2L NA V10 (shares its roots with the Lamborghini). The narrowest car in the field, with a mid-length wheelbase. Desirable: sharp turn-in, strong rotation and braking, excellent in slow and medium corners, rides kerbs well, and its narrow body helps in traffic. Undesirable: can snap on throttle or lift-off at the limit and needs a smooth right foot; less stable than front-engine cars in fast sweepers. A popular all-rounder for drivers who like a car that turns.</t>
+  </si>
+  <si>
+    <t>Front-mid 3.0L twin-turbo inline-six. Longest body and wheelbase in the field and the lightest wet weight. Very stable aero platform with strong high-speed downforce. Desirable: extremely forgiving and predictable, excellent traction and braking stability, easy on tires, a top pick for beginners and endurance racing. Undesirable: slow to rotate in tight hairpins, and its size is a handicap on narrow, twisty tracks. Shines on fast, flowing circuits.</t>
+  </si>
+  <si>
+    <t>Front-mid 5.5L NA flat-plane V8 revving to 8,000. Wide body, well-balanced front-mid layout with efficient aero and good straight-line speed. Desirable: stable and predictable, strong traction and braking, good tire life, confident in high-speed corners. Undesirable: a bit lazy on turn-in and prone to understeer in slow, tight corners compared with mid-engine cars. A strong choice for consistent drivers and power tracks.</t>
+  </si>
+  <si>
+    <t>Mid-engine 3.0L twin-turbo 120° V6 with strong torque (490 lb-ft). Heaviest car in the field, but with low center of gravity and very efficient aero. Desirable: excellent braking and turn-in, strong rotation while staying more forgiving than most mid-engine cars, good traction and high-speed stability. Undesirable: turbo torque needs managing on slow exits, and its weight shows in quick direction changes. A strong all-rounder that suits most tracks.</t>
   </si>
 </sst>
 </file>
@@ -135,10 +171,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,10 +492,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B11A3F3B-B2BE-4548-A3AF-4AC5B5F6D657}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="108.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -487,8 +530,11 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -519,8 +565,11 @@
       <c r="J2">
         <v>565</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -551,8 +600,11 @@
       <c r="J3">
         <v>500</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -583,8 +635,11 @@
       <c r="J4">
         <v>516</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -615,8 +670,11 @@
       <c r="J5">
         <v>500</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -647,8 +705,11 @@
       <c r="J6">
         <v>520</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -679,8 +740,11 @@
       <c r="J7">
         <v>520</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -711,8 +775,11 @@
       <c r="J8">
         <v>535</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K8" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -743,8 +810,11 @@
       <c r="J9">
         <v>518</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K9" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -775,8 +845,11 @@
       <c r="J10">
         <v>500</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K10" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -807,8 +880,11 @@
       <c r="J11">
         <v>520</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K11" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -838,6 +914,9 @@
       </c>
       <c r="J12">
         <v>524</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
